--- a/2022 data/excel_outputs/320_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/320_boothwise_data.xlsx
@@ -14,801 +14,1437 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="501">
   <si>
     <t>AC 320 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ######### ### ##0##01</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ######### ### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##0##01</t>
-  </si>
-  <si>
-    <t>##0 ### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0####### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##04</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##02</t>
-  </si>
-  <si>
-    <t>##### ## #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ####### ##### 1</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ####### ##### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####### #0##0##0 ###### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####### #0##0##0 ###### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>####### #0##0##0 ###### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>####### #0##0##0 ###### ##0 ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0##02</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0############ #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0####</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ##0##01</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ##0##02</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ##0##03</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ##0##04</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0##01</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0##02</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0##03</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0##04</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0##05</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ######## ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0##02</t>
-  </si>
-  <si>
-    <t>#### #0##0 ######## ##0##01</t>
-  </si>
-  <si>
-    <t>#### #0##0 ######## ##0##02</t>
-  </si>
-  <si>
-    <t>#### #0##0 ######## ##0##03</t>
-  </si>
-  <si>
-    <t>#### #0##0 ######## ##0##04</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## ##0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## ##0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## ##0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## ##0##04</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #0#01</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #0#02</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #0#03</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######## #0#04</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ###### #0##01</t>
-  </si>
-  <si>
-    <t>#0##0 ######## ###### #0##02</t>
-  </si>
-  <si>
-    <t>#0##0 ######## e###### #0##03</t>
-  </si>
-  <si>
-    <t>#0##0 ######## e###### #0##0 4</t>
-  </si>
-  <si>
-    <t>####### ##### #0##0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ########## #### #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ########## #### #### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ########## #### #### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ########## #### #### ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ########## #### #### ###### #0##0 5</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0#### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0#### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##04</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##05</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ##### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ##### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ##### ##0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ##### ##0##0 4</t>
-  </si>
-  <si>
-    <t>##### ###### ########### ##### 1</t>
-  </si>
-  <si>
-    <t>##### ###### ########### ##### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ########## #0##01</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ########## ##0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ########## ##0##0 4</t>
-  </si>
-  <si>
-    <t>#0##0##0##0#0##0##0####### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0 ### #######</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ######## #0##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ######## #0##0 4</t>
-  </si>
-  <si>
-    <t>####0### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0##04</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##01</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##02</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##03</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##04</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##05</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##06</t>
-  </si>
-  <si>
-    <t>### ###### #0##0 ##### #0##07</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ########## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ########## #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ########## #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0##03</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ##### #0##0 5</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ####### #0##0</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###### #0##05</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #0##02</t>
-  </si>
-  <si>
-    <t>####0## ########</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ### #0##02</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### #0##01</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### #0##02</t>
-  </si>
-  <si>
-    <t>### #### #0##0##0 #### #0##0 1</t>
-  </si>
-  <si>
-    <t>### #### #0#0##0 #### #0##0 2</t>
-  </si>
-  <si>
-    <t>### #### #0#0##0 #### #0##0 3</t>
-  </si>
-  <si>
-    <t>###### ### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0##04</t>
-  </si>
-  <si>
-    <t>###### ### ########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #0##01</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #0##02</t>
-  </si>
-  <si>
-    <t>##### ##### #0 ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>###### ### ####</t>
-  </si>
-  <si>
-    <t>###### ### #####</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ##### #0##01</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ##### #0##02</t>
-  </si>
-  <si>
-    <t>###### ### ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##### #### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ### ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ### ###### #0##04</t>
-  </si>
-  <si>
-    <t>##### #0##0 ###### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0## 2</t>
-  </si>
-  <si>
-    <t>####0##0 ### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ### ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### ######## #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######## #### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######## #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ## ######## #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ## ######## #### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 ## ######## #### ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0##0 ## ######## #### ###### #0##04</t>
-  </si>
-  <si>
-    <t>####0##0###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #0##0 5</t>
-  </si>
-  <si>
-    <t>###### ### ###### #### ## ###### #### #0##01</t>
-  </si>
-  <si>
-    <t>###### ### ###### #### ## ###### #### #0##02</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### #0##02</t>
-  </si>
-  <si>
-    <t>##0### #### #0##01</t>
-  </si>
-  <si>
-    <t>##0### #### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #0##01</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #0##02</t>
-  </si>
-  <si>
-    <t>###### ### ##### #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #0##0 2</t>
+    <t>A0 V0 MARAHATHA NAV MAT BHAVAN KAM0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 MARAHATHA NAV MAT BHAVAN KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BAKH RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 MEJHUKA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHADAKH DAYA KAM0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KHADAKH DAYA KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BADUA KAM0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BADUA KAM0SAM02</t>
+  </si>
+  <si>
+    <t>PAM0 BHAVAN GAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 B DOH</t>
+  </si>
+  <si>
+    <t>A0 V0 KUNAVAR KAM0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KUNAVAR KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 MOGALAHA</t>
+  </si>
+  <si>
+    <t>A0 V0JAVAI%NAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAKOLA</t>
+  </si>
+  <si>
+    <t>A0 V0 BELAMA</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAKADAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 BALAA U K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BALAA U K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 BALAA U K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAIRAT</t>
+  </si>
+  <si>
+    <t>A0 V0 DUM RAYA</t>
+  </si>
+  <si>
+    <t>BARAT GHAR BHAV U H)</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA BAJ U G U K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA BAJ U G U K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA BAJ U G U K0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA BAJ U G U K0SAM0 4</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAURA BAJ U G U K0SAM0 5</t>
+  </si>
+  <si>
+    <t>A0 V0 GAYAGHAT</t>
+  </si>
+  <si>
+    <t>A0 V0 VASHAN U PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGAUL) PARU B</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGAUL) PI-CHAM</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAISALA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVANAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAJARU GAMVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAJARU GAMVA K0SAM02</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL KHAJARU GAMVA</t>
+  </si>
+  <si>
+    <t>A0 V0 PACHAMA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 PACHAMA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAIPAR K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAIPAR K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BAHABO LAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 MAR0H RAYA</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL MAS U ABAR K0SAM0 1</t>
+  </si>
+  <si>
+    <t>J0U HA0.KULAMAS U ABAR K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 GE1I BAJ U G U</t>
+  </si>
+  <si>
+    <t>A0 V0 GE1I KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 SANAGAD K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SANAGAD K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 KAHARAUL)</t>
+  </si>
+  <si>
+    <t>A0 V0 A0HARAUL)</t>
+  </si>
+  <si>
+    <t>A0 V0POVA</t>
+  </si>
+  <si>
+    <t>A0 V0MAJHAGAMVA</t>
+  </si>
+  <si>
+    <t>A0 V0 TALABAMJARAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 GAURE YA</t>
+  </si>
+  <si>
+    <t>A0 V0 BANAKATA</t>
+  </si>
+  <si>
+    <t>A0 V0 %CHATAH) KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 KAKATAH)</t>
+  </si>
+  <si>
+    <t>I0KA0 THAKURANAGAR KAM0SAM01</t>
+  </si>
+  <si>
+    <t>I0KA0 THAKURANAGAR KAM0SAM02</t>
+  </si>
+  <si>
+    <t>I0KA0 THAKURANAGAR KAM0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 LOHARAPARU VA KAM0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 LOHARAPARU VA KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 LOHARAPARU VA KAM0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 HANUMAN NAGAR LOHARAPARU VA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 HANUMAN NAGAR LOHARAPARU VA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAPARU KAM0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAPARU KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS TAPARU KAM0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS TAPARU KAM0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS TAPARU KAM0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS TAPARU KAM0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS TAPARU KAM0SAM05</t>
+  </si>
+  <si>
+    <t>PAVU MA0 V0 BAS TAPARU KAM0SAM0 4</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAPATAHA KAM0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAPATAHA KAM0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAPATAHA KAM0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAPATAHA KAM0SAM0 4</t>
+  </si>
+  <si>
+    <t>A0 V0 MADHOPARU KAM0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 MADHOPARU KAM0SAM02</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 I DARAPARU KAM0SAM01</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 I DARAPARU KAM0SAM05</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 I DARAPARU KAM0SAM02</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 I DARAPARU KAM0SAM03</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 I DARAPARU KAM0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAGAMJ UPH HARANAMAPARU KAM0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAGAMJ UPH HARANAMAPARU KAM0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAGAMJ UPH HARANAMAPARU KAM0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUR)</t>
+  </si>
+  <si>
+    <t>A0 V0 PARASA</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL MACHAL)GAMV K0S01</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL MACHAL)GAMV K0S02</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL MACHAL)GAMV K0S03</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL MACHAL)GAMV K0S04</t>
+  </si>
+  <si>
+    <t>I0KA0 MACHAL)GAMV BARAGADAH) K0SAM01</t>
+  </si>
+  <si>
+    <t>I0KA0 MACHAL)GAMV BARAGADAH) K0SAM04</t>
+  </si>
+  <si>
+    <t>I0KA0 MACHAL)GAMV ,BARAGADAH) K0SAM02</t>
+  </si>
+  <si>
+    <t>I0KA0 MACHAL)GAMV ,BARAGADAH) K0SAM0 3</t>
+  </si>
+  <si>
+    <t>I 8A GAMDHI U0MA0 V0 KAR)MANAGAR K0SAM01</t>
+  </si>
+  <si>
+    <t>I 8A GAMDHI U0MA0 V0 KAR)MANAGAR K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 MAH U :MADAPARU UPH HAGANA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 MAH U :MADAPARU UPH HAGANA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 CH D)PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 AL)GADH K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 AL)GADH K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;MIPARU K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;MIPARU K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAURABAR) K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAURABAR) K0SAM0 2</t>
+  </si>
+  <si>
+    <t>IM0KA0 MAH U :MADAPARU UPH JAMGAL B==N K0SAM0 1</t>
+  </si>
+  <si>
+    <t>IM0KA0 MAH U :MADAPARU UPH JAMGAL B==N K0SAM0 2</t>
+  </si>
+  <si>
+    <t>IM0KA0 MAH U :MADAPARU UPH JAMGAL B==N K0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 MOHANAG K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 MOHANAG K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 ALAGATAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 ALAGATAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;:MIPARU 0D&gt;TIY K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;MIPARU M 0D&gt;TIY K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0SARU S K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0SARU S K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 SARU S K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPARU K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 KAI:PAYARANAGAR</t>
+  </si>
+  <si>
+    <t>A0 V0 ALENABAD</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUMAKH U A K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUMAKH U A K0SAM05</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUMAKH U A K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUMAKH U A K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUMAKH U A K0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 BANABHAGALAPARU K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BANABHAGALAPARU K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 JANAKAPARU K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 JANAKAPARU K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 TE DAA U VAS:BHARAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 TE DAA U VAS:BHARAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMACHAURA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMACHAURA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 KU JALAGADH</t>
+  </si>
+  <si>
+    <t>A0 V0 BAJAH)</t>
+  </si>
+  <si>
+    <t>A0 V0 BAJAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 BADASHAHAPARU</t>
+  </si>
+  <si>
+    <t>CH0 M0 V0 M0U0MA0 V0RAVATAGAM J KUI</t>
+  </si>
+  <si>
+    <t>A0 V0 KARAMAHAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 MAH U :MADAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 NAVAPAR K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 NAVAPAR K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 KHOKHAR) K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KHOKHAR) K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAVAL0HAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAVAL0HAYA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAVAPARU KARAMAHAVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAVAPARU KARAMAHAVA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 GUL RAHA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 GUL RAHA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARAV LAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARAV LAYA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>PAM0 BHAVAN RAIKABEL</t>
+  </si>
+  <si>
+    <t>|0 T0 CHAMJ|T|T CH|GHKML</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL RAMANAGAR KEVAT LAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL RAMANAGAR KEVAT LAYA K0SAM0 3</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL RAMANAGAR KEVAT LAYA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAMAPARU K0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 ALAMACHAK K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 ALAMACHAK K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHAVANAKHOR K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHAVANAKHOR K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 KAAYANAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 KAAYANAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 KAAYANAPARU K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 AKATAHAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL AGAH) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL AGAH) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL AGAH) K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL AGAH) K0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 BADH U E L) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BADH U E L) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 BADH U E L) K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 BHABHAUR K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BHABHAUR K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 BB.TAUL)</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM01</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM06</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM02</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM04</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM05</t>
+  </si>
+  <si>
+    <t>VIR SHAVAJI I0KA0 SARAHAR) K0SAM07</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;MIPARU K0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 MAKHANAHA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 MAKHANAHA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 MAKHANAHA K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGAH)BHAR) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGAH)BHAR) K0SAM02</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 1</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 5</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 2</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 3</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 4</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ THAM K0SAM0 6</t>
+  </si>
+  <si>
+    <t>A0 V0 SAHABAGAMJ NAV MAT BHAVAN K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SAHABAGAMJ NAV MAT BHAVAN K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SAHABAGAMJ THAM K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SAHABAGAMJ THAM K0SAM0 2</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ 0D&gt;TIY K0SAM0 1</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ 0D&gt;TIY K0SAM0 2</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ 0D&gt;TIY K0SAM0 3</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAHABAGAMJ 0D&gt;TIY K0SAM0 4</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL BBAHUL) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL BBAHUL) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL BBAHUL) K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL BBAHUL) K0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL JHAJHAVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL JHAJHAVA K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMGAL JHAJHAVA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAPARU K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 PACHAGAMVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 PACHAGAMVA K0SAM02</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL GOPALAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 DHE DHANA</t>
+  </si>
+  <si>
+    <t>A0 V0 NU1DINACHAK</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIJANATHAPARU</t>
+  </si>
+  <si>
+    <t>A0 V JAGAD)SHAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAKHAKH U OR K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAKHAKH U OR K0SAM02</t>
+  </si>
+  <si>
+    <t>PAV U 0MA0 V0 RAKHAKH U OR K0SAM01</t>
+  </si>
+  <si>
+    <t>PAV U 0MA0 V0 RAKHAKH U OR K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 CHET RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAN K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BAN K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 JALAR K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 0H1A</t>
+  </si>
+  <si>
+    <t>A0 V0 MAJHAUNA</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAKHOR)</t>
+  </si>
+  <si>
+    <t>J0U HA0.KUL PHARADAHANI K0SAM01</t>
+  </si>
+  <si>
+    <t>J0U HA0.KUL PHARADAHANI K0SAM02</t>
+  </si>
+  <si>
+    <t>J0U HA0.KUL PHARADAHANI K0SAM03</t>
+  </si>
+  <si>
+    <t>A0 V0 L&lt;MIPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 TE DHAVIR</t>
+  </si>
+  <si>
+    <t>AMAR SAMH U0MA0 V0 BADHAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>AMAR SAMH U0M0 V0 BADHAYA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>AMAR SAMH U0M0 V0 BADHAYA K0SAM0 3</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN CHAUKAMAPHAE</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAI U DHARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 PHAIJALAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RANADIH</t>
+  </si>
+  <si>
+    <t>A0 V0 MADAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 SAMKHI</t>
+  </si>
+  <si>
+    <t>J0U HA0 SAMKHI</t>
+  </si>
+  <si>
+    <t>A0 V0 KARATAHAR) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 KARATAHAR) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 MAMJH RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 JASAVAL</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJABAR) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJABAR) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJABAR) K0SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJABAR) K0SAM04</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIRAGHATATA</t>
+  </si>
+  <si>
+    <t>A0 V0 ITAVA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN BARAHAPAT)</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL BHIT) K0SAM01</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL BHIT) K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 DADHADIH</t>
+  </si>
+  <si>
+    <t>-YAM KRRIGN I0 KA0 THAVAIPAR</t>
+  </si>
+  <si>
+    <t>A0 V0 DAHAVA BAJ U G U</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAGH U AT</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU KAITHAV LAYA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU KAITHAV LAYA K0SAM02</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN NIBA</t>
+  </si>
+  <si>
+    <t>A0 V0 KANAPAR</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN BARAHATA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARO0HAYA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARO0HAYA K0SAM02</t>
+  </si>
+  <si>
+    <t>K YA A0 V0 %TAGHARA K0SAM01</t>
+  </si>
+  <si>
+    <t>K YA A0 V0 %TAGHARA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 %TAGHARA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 %TAGHARA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 %TAGHARA K0SAM03</t>
+  </si>
+  <si>
+    <t>A0PA0 KOAHUA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 KOAHUA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0 V0 NAINASAR</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN RASAL U PARU CHAIKAYA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN JARAHAD</t>
+  </si>
+  <si>
+    <t>A0PA0 TUKAV LAYA AM SHAK PARU B</t>
+  </si>
+  <si>
+    <t>A0PA0 TUKAVA LAYA AM0</t>
+  </si>
+  <si>
+    <t>IKASAN I0KA0 ABHARU AM</t>
+  </si>
+  <si>
+    <t>A0PA0 BELAGHAT KHAD U PI-CHAMI</t>
+  </si>
+  <si>
+    <t>A0PA0 BELAGHAT KHAD U PAV U J</t>
+  </si>
+  <si>
+    <t>A0VA0 SAMGAHA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 M0TAYAR) K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 PHULAV RAYA U&gt;TAR</t>
+  </si>
+  <si>
+    <t>A0PA0 PHULAV RAYA K0SAM 2</t>
+  </si>
+  <si>
+    <t>A0PA0 TAL LAKKHAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 MOH:MADAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MADAHA GOKUL)</t>
+  </si>
+  <si>
+    <t>A0PA0 NAYAGAMV K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 NAYAGAMV K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 PARU B PARU ANI BBIADAGAM JAMGAL KAU DAYA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 PARU ANI BBIADAGAM JAMGAL KAU DAYA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 PARU ANI BBIADAGAM JAMGAL KAU DAYA K0SAM03</t>
+  </si>
+  <si>
+    <t>A0PA0 NAI BBIADAGAM JAMGAL KAU DAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 NAI BBIADAGAM JAMGAL KAU DAYA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 NAI BBIADAGAM JAMGAL KAU DAYA K0SAM03</t>
+  </si>
+  <si>
+    <t>A0PA0 NAI BBIADAGAM JAMGAL KAU DAYA K0SAM04</t>
+  </si>
+  <si>
+    <t>A0PA0 LCHAUTAHA</t>
+  </si>
+  <si>
+    <t>A0PA0 GAYAGHAT</t>
+  </si>
+  <si>
+    <t>A0PA0 KAR0HAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 IJ DAPARU K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 IJ DAPARU K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 DIHAGHAT PARU B</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN LCHAUT)JAM</t>
+  </si>
+  <si>
+    <t>A0PA0 A0HARAUL) PARU B</t>
+  </si>
+  <si>
+    <t>A0PA0 A0HARAUL) PI-CHAM</t>
+  </si>
+  <si>
+    <t>A0PA0 SAKHI UPH MEHAD RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 SAMHORAVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 SAMHORAVA K0SAM02</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL SAMHORAVA</t>
+  </si>
+  <si>
+    <t>A0PA0 BAN0TAKULA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN KEVAT LAYA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN BALAA U</t>
+  </si>
+  <si>
+    <t>A0PA0 AJIJAA U LAH UPH CHAIKAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 TAPAPARU K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 TAPAPARU K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 KU.DAVA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 KU.DAVA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 MAINABHAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0 MIRAPARU U&gt;TAR</t>
+  </si>
+  <si>
+    <t>A0PA0 MIRAPARU DANON</t>
+  </si>
+  <si>
+    <t>A0PA0 U.KA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 U.KA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 DAHALA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 DAHALA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 BAURADIH</t>
+  </si>
+  <si>
+    <t>A0PA0 B RAYARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 TARAM GACHAK</t>
+  </si>
+  <si>
+    <t>A0PA0 B0U DHAYABAR) ़</t>
+  </si>
+  <si>
+    <t>A0PA0 KAJIPARU</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL DOH RAYA K0SAM0 1</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL DOH RAYA K0SAM0 2</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL DOH RAYA K0SAM0 3</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL DOH RAYA K0SAM0 4</t>
+  </si>
+  <si>
+    <t>J0U HA0 .KUL DOH RAYA K0SAM0 5</t>
+  </si>
+  <si>
+    <t>A0PA0 AVAIPAKAD K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 KAR JAHAVA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN BHAURAMAL UPH NAI KALONI K0SAM01</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN BHAURAMAL UPH NAI KALONI K0SAM02</t>
+  </si>
+  <si>
+    <t>PAV U MA0 V0 BELAPAR UPH GU1NAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0 MAH U :MADAPARU MAPHAE K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 MAH U :MADAPARU MAPHAE K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 KOTHA</t>
+  </si>
+  <si>
+    <t>A0PA0 JAMAA U D</t>
+  </si>
+  <si>
+    <t>A0PA0 TAJADIH</t>
+  </si>
+  <si>
+    <t>PAM0BHAVAN BELA</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJHAGAMVA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 GAURA KHAS K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 GAURAKHAS K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 GHUNAGHUNAKOTHA K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 GHUNAGHUNAKOTHA K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 DO MANAGADH K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 DO MANAGADH K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 MAMJH RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 SEMARA</t>
+  </si>
+  <si>
+    <t>A0PA0 U&gt;TARASOT K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 U&gt;TARASOT K0SAM02</t>
+  </si>
+  <si>
+    <t>KL0THATHABHKL0 SHRATHABHDYAJBH|THABHS|THABHSHRCH|KL|SHRAJ AIBHTBBH0DYACHKL|J~N01</t>
+  </si>
+  <si>
+    <t>KL0THATHABHKL0 SHRATHABHDYAJBH|THABHS|THABHSHRCH|KL|SHRAJ AIBHTBBH0DYACHKL|J~N02</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN KALANI UPH</t>
+  </si>
+  <si>
+    <t>BADHANI A0PA0 BHATANI K0SAM01</t>
+  </si>
+  <si>
+    <t>A0PA0 BHATANI K0SAM02</t>
+  </si>
+  <si>
+    <t>A0PA0 SHERAPARU CHAMARAH K0SAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 SHERAPARU CHAMARAH K0SAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
+  </si>
+  <si>
+    <t>A0PA0 KUSHAHARA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 461</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -887,8 +1523,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -904,7 +1548,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -912,12 +1556,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1216,88 +1878,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>477</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>478</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>479</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>480</v>
       </c>
       <c r="G2" t="s">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="H2" t="s">
-        <v>270</v>
+        <v>482</v>
       </c>
       <c r="I2" t="s">
-        <v>271</v>
+        <v>483</v>
       </c>
       <c r="J2" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="K2" t="s">
-        <v>273</v>
+        <v>485</v>
       </c>
       <c r="L2" t="s">
-        <v>274</v>
+        <v>486</v>
       </c>
       <c r="M2" t="s">
-        <v>275</v>
+        <v>487</v>
       </c>
       <c r="N2" t="s">
-        <v>276</v>
+        <v>488</v>
       </c>
       <c r="O2" t="s">
-        <v>277</v>
+        <v>489</v>
       </c>
       <c r="P2" t="s">
-        <v>278</v>
+        <v>490</v>
       </c>
       <c r="Q2" t="s">
-        <v>279</v>
+        <v>491</v>
       </c>
       <c r="R2" t="s">
-        <v>280</v>
+        <v>492</v>
       </c>
       <c r="S2" t="s">
-        <v>281</v>
+        <v>493</v>
       </c>
       <c r="T2" t="s">
-        <v>282</v>
+        <v>494</v>
       </c>
       <c r="U2" t="s">
-        <v>283</v>
+        <v>495</v>
       </c>
       <c r="V2" t="s">
-        <v>284</v>
+        <v>496</v>
       </c>
       <c r="W2" t="s">
-        <v>285</v>
+        <v>497</v>
       </c>
       <c r="X2" t="s">
-        <v>286</v>
+        <v>498</v>
       </c>
       <c r="Y2" t="s">
-        <v>287</v>
+        <v>499</v>
       </c>
       <c r="Z2" t="s">
-        <v>288</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1305,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1158</v>
@@ -1385,7 +2122,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>802</v>
@@ -1465,7 +2202,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>705</v>
@@ -1545,7 +2282,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>485</v>
@@ -1625,7 +2362,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>851</v>
@@ -1705,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>810</v>
@@ -1785,7 +2522,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>539</v>
@@ -1865,7 +2602,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>699</v>
@@ -1945,7 +2682,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>1116</v>
@@ -2025,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1137</v>
@@ -2105,7 +2842,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>475</v>
@@ -2185,7 +2922,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>604</v>
@@ -2265,7 +3002,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>612</v>
@@ -2345,7 +3082,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>772</v>
@@ -2425,7 +3162,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>587</v>
@@ -2505,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>947</v>
@@ -2585,7 +3322,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>634</v>
@@ -2665,7 +3402,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>725</v>
@@ -2745,7 +3482,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>629</v>
@@ -2825,7 +3562,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>623</v>
@@ -2905,7 +3642,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>404</v>
@@ -2985,7 +3722,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>821</v>
@@ -3065,7 +3802,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>507</v>
@@ -3145,7 +3882,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>623</v>
@@ -3225,7 +3962,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>1094</v>
@@ -3305,7 +4042,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>1019</v>
@@ -3385,7 +4122,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>781</v>
@@ -3465,7 +4202,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>588</v>
@@ -3545,7 +4282,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>481</v>
@@ -3625,7 +4362,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>774</v>
@@ -3705,7 +4442,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>843</v>
@@ -3785,7 +4522,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>818</v>
@@ -3865,7 +4602,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>399</v>
@@ -3945,7 +4682,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>836</v>
@@ -4025,7 +4762,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>799</v>
@@ -4105,7 +4842,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>601</v>
@@ -4185,7 +4922,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>724</v>
@@ -4265,7 +5002,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>975</v>
@@ -4345,7 +5082,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>1014</v>
@@ -4425,7 +5162,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>795</v>
@@ -4505,7 +5242,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>824</v>
@@ -4585,7 +5322,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>795</v>
@@ -4665,7 +5402,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>449</v>
@@ -4745,7 +5482,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>856</v>
@@ -4825,7 +5562,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>428</v>
@@ -4905,7 +5642,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>990</v>
@@ -4985,7 +5722,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>821</v>
@@ -5065,7 +5802,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>1027</v>
@@ -5145,7 +5882,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>1069</v>
@@ -5225,7 +5962,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>605</v>
@@ -5305,7 +6042,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>633</v>
@@ -5385,7 +6122,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>1052</v>
@@ -5465,7 +6202,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>1031</v>
@@ -5545,7 +6282,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>997</v>
@@ -5625,7 +6362,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>819</v>
@@ -5705,7 +6442,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>500</v>
@@ -5785,7 +6522,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>722</v>
@@ -5865,7 +6602,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>711</v>
@@ -5945,7 +6682,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>1107</v>
@@ -6025,7 +6762,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>982</v>
@@ -6105,7 +6842,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>632</v>
@@ -6185,7 +6922,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>956</v>
@@ -6265,7 +7002,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>1066</v>
@@ -6345,7 +7082,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>1082</v>
@@ -6425,7 +7162,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>681</v>
@@ -6505,7 +7242,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>527</v>
@@ -6585,7 +7322,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>805</v>
@@ -6665,7 +7402,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>764</v>
@@ -6745,7 +7482,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>510</v>
@@ -6825,7 +7562,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>638</v>
@@ -6905,7 +7642,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>693</v>
@@ -6985,7 +7722,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>526</v>
@@ -7065,7 +7802,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>1017</v>
@@ -7145,7 +7882,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>932</v>
@@ -7225,7 +7962,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>335</v>
@@ -7305,7 +8042,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>794</v>
@@ -7385,7 +8122,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>1094</v>
@@ -7465,7 +8202,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>989</v>
@@ -7545,7 +8282,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>1138</v>
@@ -7625,7 +8362,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>1064</v>
@@ -7705,7 +8442,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>641</v>
@@ -7785,7 +8522,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>1105</v>
@@ -7865,7 +8602,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>770</v>
@@ -7945,7 +8682,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>673</v>
@@ -8025,7 +8762,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>986</v>
@@ -8105,7 +8842,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>991</v>
@@ -8185,7 +8922,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>1027</v>
@@ -8265,7 +9002,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>753</v>
@@ -8345,7 +9082,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>1006</v>
@@ -8425,7 +9162,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>936</v>
@@ -8505,7 +9242,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>1109</v>
@@ -8585,7 +9322,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C94">
         <v>1152</v>
@@ -8665,7 +9402,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>1059</v>
@@ -8745,7 +9482,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>907</v>
@@ -8825,7 +9562,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>1118</v>
@@ -8905,7 +9642,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>630</v>
@@ -8985,7 +9722,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>950</v>
@@ -9065,7 +9802,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>986</v>
@@ -9145,7 +9882,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>756</v>
@@ -9225,7 +9962,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>868</v>
@@ -9305,7 +10042,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>945</v>
@@ -9385,7 +10122,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>786</v>
@@ -9465,7 +10202,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>732</v>
@@ -9545,7 +10282,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>786</v>
@@ -9625,7 +10362,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>806</v>
@@ -9705,7 +10442,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>804</v>
@@ -9785,7 +10522,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>837</v>
@@ -9865,7 +10602,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>780</v>
@@ -9945,7 +10682,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>1032</v>
@@ -10025,7 +10762,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>826</v>
@@ -10105,7 +10842,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>743</v>
@@ -10185,7 +10922,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>655</v>
@@ -10265,7 +11002,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>565</v>
@@ -10345,7 +11082,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>878</v>
@@ -10425,7 +11162,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>998</v>
@@ -10505,7 +11242,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>774</v>
@@ -10585,7 +11322,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>764</v>
@@ -10665,7 +11402,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>923</v>
@@ -10745,7 +11482,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>683</v>
@@ -10825,7 +11562,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>839</v>
@@ -10905,7 +11642,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>800</v>
@@ -10985,7 +11722,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>760</v>
@@ -11065,7 +11802,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>1035</v>
@@ -11145,7 +11882,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>876</v>
@@ -11225,7 +11962,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>672</v>
@@ -11305,7 +12042,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>537</v>
@@ -11385,7 +12122,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>1080</v>
@@ -11465,7 +12202,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>951</v>
@@ -11545,7 +12282,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>1011</v>
@@ -11625,7 +12362,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>596</v>
@@ -11705,7 +12442,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>596</v>
@@ -11785,7 +12522,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>906</v>
@@ -11865,7 +12602,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>544</v>
@@ -11945,7 +12682,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>642</v>
@@ -12025,7 +12762,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>1130</v>
@@ -12105,7 +12842,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>1109</v>
@@ -12185,7 +12922,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>788</v>
@@ -12265,7 +13002,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>795</v>
@@ -12345,7 +13082,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>526</v>
@@ -12425,7 +13162,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>741</v>
@@ -12505,7 +13242,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>986</v>
@@ -12585,7 +13322,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>1023</v>
@@ -12665,7 +13402,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>1109</v>
@@ -12745,7 +13482,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>741</v>
@@ -12825,7 +13562,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>764</v>
@@ -12905,7 +13642,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>984</v>
@@ -12985,7 +13722,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>860</v>
@@ -13065,7 +13802,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>1056</v>
@@ -13145,7 +13882,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>754</v>
@@ -13225,7 +13962,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>812</v>
@@ -13305,7 +14042,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>929</v>
@@ -13385,7 +14122,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>618</v>
@@ -13465,7 +14202,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>721</v>
@@ -13545,7 +14282,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>754</v>
@@ -13625,7 +14362,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>958</v>
@@ -13705,7 +14442,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>1030</v>
@@ -13785,7 +14522,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>674</v>
@@ -13865,7 +14602,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>631</v>
@@ -13945,7 +14682,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>1181</v>
@@ -14025,7 +14762,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>854</v>
@@ -14105,7 +14842,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>965</v>
@@ -14185,7 +14922,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>926</v>
@@ -14265,7 +15002,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>1001</v>
@@ -14345,7 +15082,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>564</v>
@@ -14425,7 +15162,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>763</v>
@@ -14505,7 +15242,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>972</v>
@@ -14585,7 +15322,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>1107</v>
@@ -14665,7 +15402,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>1007</v>
@@ -14745,7 +15482,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>687</v>
@@ -14825,7 +15562,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>671</v>
@@ -14905,7 +15642,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>741</v>
@@ -14985,7 +15722,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>632</v>
@@ -15065,7 +15802,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>698</v>
@@ -15145,7 +15882,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>716</v>
@@ -15225,7 +15962,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>681</v>
@@ -15305,7 +16042,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>548</v>
@@ -15385,7 +16122,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>1087</v>
@@ -15465,7 +16202,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>967</v>
@@ -15545,7 +16282,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>704</v>
@@ -15625,7 +16362,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>888</v>
@@ -15705,7 +16442,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>1051</v>
@@ -15785,7 +16522,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>64</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>730</v>
@@ -15865,7 +16602,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>457</v>
@@ -15945,7 +16682,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>846</v>
@@ -16025,7 +16762,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>684</v>
@@ -16105,7 +16842,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>886</v>
@@ -16185,7 +16922,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>691</v>
@@ -16265,7 +17002,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>547</v>
@@ -16345,7 +17082,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>1175</v>
@@ -16425,7 +17162,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>618</v>
@@ -16505,7 +17242,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>666</v>
@@ -16585,7 +17322,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>1112</v>
@@ -16665,7 +17402,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>839</v>
@@ -16745,7 +17482,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>655</v>
@@ -16825,7 +17562,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C197">
         <v>745</v>
@@ -16905,7 +17642,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C198">
         <v>905</v>
@@ -16985,7 +17722,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>920</v>
@@ -17065,7 +17802,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>669</v>
@@ -17145,7 +17882,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>1014</v>
@@ -17225,7 +17962,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>834</v>
@@ -17305,7 +18042,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>714</v>
@@ -17385,7 +18122,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>261</v>
@@ -17465,7 +18202,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>812</v>
@@ -17545,7 +18282,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>990</v>
@@ -17625,7 +18362,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>635</v>
@@ -17705,7 +18442,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>580</v>
@@ -17785,7 +18522,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>26</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>799</v>
@@ -17865,7 +18602,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>831</v>
@@ -17945,7 +18682,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>118</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>744</v>
@@ -18025,7 +18762,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>910</v>
@@ -18105,7 +18842,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>1108</v>
@@ -18185,7 +18922,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>784</v>
@@ -18265,7 +19002,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>931</v>
@@ -18345,7 +19082,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>1111</v>
@@ -18425,7 +19162,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>648</v>
@@ -18505,7 +19242,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>42</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>584</v>
@@ -18585,7 +19322,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>1079</v>
@@ -18665,7 +19402,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>942</v>
@@ -18745,7 +19482,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>658</v>
@@ -18825,7 +19562,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>35</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>666</v>
@@ -18905,7 +19642,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>972</v>
@@ -18985,7 +19722,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>1091</v>
@@ -19065,7 +19802,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>1036</v>
@@ -19145,7 +19882,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>744</v>
@@ -19225,7 +19962,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>954</v>
@@ -19305,7 +20042,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>125</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>883</v>
@@ -19385,7 +20122,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>126</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>922</v>
@@ -19465,7 +20202,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>705</v>
@@ -19545,7 +20282,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>1010</v>
@@ -19625,7 +20362,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>1080</v>
@@ -19705,7 +20442,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>155</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>817</v>
@@ -19785,7 +20522,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>803</v>
@@ -19865,7 +20602,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>911</v>
@@ -19945,7 +20682,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>733</v>
@@ -20025,7 +20762,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>563</v>
@@ -20105,7 +20842,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>941</v>
@@ -20185,7 +20922,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>933</v>
@@ -20265,7 +21002,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>771</v>
@@ -20345,7 +21082,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>168</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>898</v>
@@ -20425,7 +21162,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>169</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>657</v>
@@ -20505,7 +21242,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>637</v>
@@ -20585,7 +21322,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>1077</v>
@@ -20665,7 +21402,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>1003</v>
@@ -20745,7 +21482,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>942</v>
@@ -20825,7 +21562,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>1099</v>
@@ -20905,7 +21642,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>753</v>
@@ -20985,7 +21722,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>960</v>
@@ -21065,7 +21802,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>156</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>813</v>
@@ -21145,7 +21882,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>721</v>
@@ -21225,7 +21962,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>830</v>
@@ -21305,7 +22042,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>907</v>
@@ -21385,7 +22122,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>176</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>905</v>
@@ -21465,7 +22202,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>177</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>714</v>
@@ -21545,7 +22282,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="C256">
         <v>927</v>
@@ -21625,7 +22362,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="C257">
         <v>977</v>
@@ -21705,7 +22442,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="C258">
         <v>777</v>
@@ -21785,7 +22522,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>181</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>771</v>
@@ -21865,7 +22602,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>1145</v>
@@ -21945,7 +22682,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>183</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>661</v>
@@ -22025,7 +22762,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>689</v>
@@ -22105,7 +22842,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>185</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>540</v>
@@ -22185,7 +22922,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>186</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>666</v>
@@ -22265,7 +23002,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>186</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>614</v>
@@ -22345,7 +23082,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>187</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>1090</v>
@@ -22425,7 +23162,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>871</v>
@@ -22505,7 +23242,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>1029</v>
@@ -22585,7 +23322,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>932</v>
@@ -22665,7 +23402,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>191</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>822</v>
@@ -22745,7 +23482,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>192</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>1025</v>
@@ -22825,7 +23562,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>193</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>1021</v>
@@ -22905,7 +23642,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>158</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>868</v>
@@ -22985,7 +23722,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>628</v>
@@ -23065,7 +23802,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>611</v>
@@ -23145,7 +23882,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>860</v>
@@ -23225,7 +23962,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>19</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>809</v>
@@ -23305,7 +24042,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>172</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>706</v>
@@ -23385,7 +24122,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>701</v>
@@ -23465,7 +24202,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>909</v>
@@ -23545,7 +24282,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>27</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>1029</v>
@@ -23625,7 +24362,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>194</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>933</v>
@@ -23705,7 +24442,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>581</v>
@@ -23785,7 +24522,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>699</v>
@@ -23865,7 +24602,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>196</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>691</v>
@@ -23945,7 +24682,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>1209</v>
@@ -24025,7 +24762,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>1007</v>
@@ -24105,7 +24842,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>26</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>984</v>
@@ -24185,7 +24922,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>27</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>1065</v>
@@ -24265,7 +25002,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>1098</v>
@@ -24345,7 +25082,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>788</v>
@@ -24425,7 +25162,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>757</v>
@@ -24505,7 +25242,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>17</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>648</v>
@@ -24585,7 +25322,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>199</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>1070</v>
@@ -24665,7 +25402,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>200</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>805</v>
@@ -24745,7 +25482,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>738</v>
@@ -24825,7 +25562,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>875</v>
@@ -24905,7 +25642,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>1106</v>
@@ -24985,7 +25722,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>956</v>
@@ -25065,7 +25802,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>201</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>1151</v>
@@ -25145,7 +25882,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>202</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>1091</v>
@@ -25225,7 +25962,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>144</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>522</v>
@@ -25305,7 +26042,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>17</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>808</v>
@@ -25385,7 +26122,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>203</v>
+        <v>322</v>
       </c>
       <c r="C304">
         <v>1055</v>
@@ -25465,7 +26202,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>204</v>
+        <v>323</v>
       </c>
       <c r="C305">
         <v>726</v>
@@ -25545,7 +26282,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>205</v>
+        <v>324</v>
       </c>
       <c r="C306">
         <v>609</v>
@@ -25625,7 +26362,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>206</v>
+        <v>325</v>
       </c>
       <c r="C307">
         <v>961</v>
@@ -25705,7 +26442,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="C308">
         <v>1010</v>
@@ -25785,7 +26522,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
       <c r="C309">
         <v>1070</v>
@@ -25865,7 +26602,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="C310">
         <v>1014</v>
@@ -25945,7 +26682,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>148</v>
+        <v>329</v>
       </c>
       <c r="C311">
         <v>662</v>
@@ -26025,7 +26762,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>147</v>
+        <v>330</v>
       </c>
       <c r="C312">
         <v>559</v>
@@ -26105,7 +26842,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>92</v>
+        <v>330</v>
       </c>
       <c r="C313">
         <v>1036</v>
@@ -26185,7 +26922,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="C314">
         <v>710</v>
@@ -26265,7 +27002,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>106</v>
+        <v>332</v>
       </c>
       <c r="C315">
         <v>569</v>
@@ -26345,7 +27082,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>208</v>
+        <v>333</v>
       </c>
       <c r="C316">
         <v>731</v>
@@ -26425,7 +27162,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>124</v>
+        <v>334</v>
       </c>
       <c r="C317">
         <v>1172</v>
@@ -26505,7 +27242,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>125</v>
+        <v>335</v>
       </c>
       <c r="C318">
         <v>765</v>
@@ -26585,7 +27322,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>125</v>
+        <v>336</v>
       </c>
       <c r="C319">
         <v>499</v>
@@ -26665,7 +27402,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>17</v>
+        <v>336</v>
       </c>
       <c r="C320">
         <v>919</v>
@@ -26745,7 +27482,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>92</v>
+        <v>337</v>
       </c>
       <c r="C321">
         <v>1060</v>
@@ -26825,7 +27562,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>155</v>
+        <v>338</v>
       </c>
       <c r="C322">
         <v>915</v>
@@ -26905,7 +27642,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>156</v>
+        <v>339</v>
       </c>
       <c r="C323">
         <v>726</v>
@@ -26985,7 +27722,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>209</v>
+        <v>340</v>
       </c>
       <c r="C324">
         <v>730</v>
@@ -27065,7 +27802,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>210</v>
+        <v>341</v>
       </c>
       <c r="C325">
         <v>1060</v>
@@ -27145,7 +27882,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>17</v>
+        <v>342</v>
       </c>
       <c r="C326">
         <v>893</v>
@@ -27225,7 +27962,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>92</v>
+        <v>343</v>
       </c>
       <c r="C327">
         <v>654</v>
@@ -27305,7 +28042,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="C328">
         <v>556</v>
@@ -27385,7 +28122,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>212</v>
+        <v>345</v>
       </c>
       <c r="C329">
         <v>680</v>
@@ -27465,7 +28202,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>213</v>
+        <v>346</v>
       </c>
       <c r="C330">
         <v>638</v>
@@ -27545,7 +28282,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>26</v>
+        <v>347</v>
       </c>
       <c r="C331">
         <v>579</v>
@@ -27625,7 +28362,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="C332">
         <v>656</v>
@@ -27705,7 +28442,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="C333">
         <v>984</v>
@@ -27785,7 +28522,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="C334">
         <v>481</v>
@@ -27865,7 +28602,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
       <c r="C335">
         <v>1006</v>
@@ -27945,7 +28682,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="C336">
         <v>717</v>
@@ -28025,7 +28762,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>118</v>
+        <v>353</v>
       </c>
       <c r="C337">
         <v>563</v>
@@ -28105,7 +28842,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>26</v>
+        <v>354</v>
       </c>
       <c r="C338">
         <v>746</v>
@@ -28185,7 +28922,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>147</v>
+        <v>355</v>
       </c>
       <c r="C339">
         <v>730</v>
@@ -28265,7 +29002,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="C340">
         <v>1070</v>
@@ -28345,7 +29082,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="C341">
         <v>644</v>
@@ -28425,7 +29162,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>17</v>
+        <v>358</v>
       </c>
       <c r="C342">
         <v>680</v>
@@ -28505,7 +29242,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>217</v>
+        <v>359</v>
       </c>
       <c r="C343">
         <v>905</v>
@@ -28585,7 +29322,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>26</v>
+        <v>360</v>
       </c>
       <c r="C344">
         <v>749</v>
@@ -28665,7 +29402,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>27</v>
+        <v>361</v>
       </c>
       <c r="C345">
         <v>628</v>
@@ -28745,7 +29482,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>218</v>
+        <v>362</v>
       </c>
       <c r="C346">
         <v>903</v>
@@ -28825,7 +29562,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>219</v>
+        <v>363</v>
       </c>
       <c r="C347">
         <v>808</v>
@@ -28905,7 +29642,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>18</v>
+        <v>364</v>
       </c>
       <c r="C348">
         <v>928</v>
@@ -28985,7 +29722,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>19</v>
+        <v>365</v>
       </c>
       <c r="C349">
         <v>829</v>
@@ -29065,7 +29802,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="C350">
         <v>774</v>
@@ -29145,7 +29882,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>26</v>
+        <v>367</v>
       </c>
       <c r="C351">
         <v>825</v>
@@ -29225,7 +29962,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="C352">
         <v>971</v>
@@ -29305,7 +30042,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="C353">
         <v>1025</v>
@@ -29385,7 +30122,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>124</v>
+        <v>370</v>
       </c>
       <c r="C354">
         <v>708</v>
@@ -29465,7 +30202,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>124</v>
+        <v>371</v>
       </c>
       <c r="C355">
         <v>687</v>
@@ -29545,7 +30282,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>125</v>
+        <v>372</v>
       </c>
       <c r="C356">
         <v>647</v>
@@ -29625,7 +30362,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>125</v>
+        <v>373</v>
       </c>
       <c r="C357">
         <v>660</v>
@@ -29705,7 +30442,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>220</v>
+        <v>373</v>
       </c>
       <c r="C358">
         <v>993</v>
@@ -29785,7 +30522,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>216</v>
+        <v>374</v>
       </c>
       <c r="C359">
         <v>736</v>
@@ -29865,7 +30602,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>221</v>
+        <v>374</v>
       </c>
       <c r="C360">
         <v>804</v>
@@ -29945,7 +30682,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>222</v>
+        <v>375</v>
       </c>
       <c r="C361">
         <v>824</v>
@@ -30025,7 +30762,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>223</v>
+        <v>376</v>
       </c>
       <c r="C362">
         <v>928</v>
@@ -30105,7 +30842,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>224</v>
+        <v>377</v>
       </c>
       <c r="C363">
         <v>830</v>
@@ -30185,7 +30922,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="C364">
         <v>1054</v>
@@ -30265,7 +31002,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>226</v>
+        <v>379</v>
       </c>
       <c r="C365">
         <v>1146</v>
@@ -30345,7 +31082,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="C366">
         <v>796</v>
@@ -30425,7 +31162,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>228</v>
+        <v>381</v>
       </c>
       <c r="C367">
         <v>712</v>
@@ -30505,7 +31242,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>26</v>
+        <v>382</v>
       </c>
       <c r="C368">
         <v>802</v>
@@ -30585,7 +31322,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>155</v>
+        <v>383</v>
       </c>
       <c r="C369">
         <v>941</v>
@@ -30665,7 +31402,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>229</v>
+        <v>384</v>
       </c>
       <c r="C370">
         <v>896</v>
@@ -30745,7 +31482,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="C371">
         <v>1048</v>
@@ -30825,7 +31562,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>231</v>
+        <v>386</v>
       </c>
       <c r="C372">
         <v>694</v>
@@ -30905,7 +31642,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>144</v>
+        <v>387</v>
       </c>
       <c r="C373">
         <v>1047</v>
@@ -30985,7 +31722,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>232</v>
+        <v>388</v>
       </c>
       <c r="C374">
         <v>541</v>
@@ -31065,7 +31802,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>26</v>
+        <v>389</v>
       </c>
       <c r="C375">
         <v>965</v>
@@ -31145,7 +31882,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>147</v>
+        <v>390</v>
       </c>
       <c r="C376">
         <v>933</v>
@@ -31225,7 +31962,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>233</v>
+        <v>391</v>
       </c>
       <c r="C377">
         <v>997</v>
@@ -31305,7 +32042,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>234</v>
+        <v>392</v>
       </c>
       <c r="C378">
         <v>983</v>
@@ -31385,7 +32122,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="C379">
         <v>954</v>
@@ -31465,7 +32202,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>234</v>
+        <v>394</v>
       </c>
       <c r="C380">
         <v>778</v>
@@ -31545,7 +32282,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>236</v>
+        <v>395</v>
       </c>
       <c r="C381">
         <v>901</v>
@@ -31625,7 +32362,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>237</v>
+        <v>396</v>
       </c>
       <c r="C382">
         <v>939</v>
@@ -31705,7 +32442,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="C383">
         <v>780</v>
@@ -31785,7 +32522,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
       <c r="C384">
         <v>877</v>
@@ -31865,7 +32602,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>45</v>
+        <v>398</v>
       </c>
       <c r="C385">
         <v>636</v>
@@ -31945,7 +32682,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>240</v>
+        <v>399</v>
       </c>
       <c r="C386">
         <v>635</v>
@@ -32025,7 +32762,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>35</v>
+        <v>400</v>
       </c>
       <c r="C387">
         <v>878</v>
@@ -32105,7 +32842,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>35</v>
+        <v>401</v>
       </c>
       <c r="C388">
         <v>533</v>
@@ -32185,7 +32922,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>136</v>
+        <v>402</v>
       </c>
       <c r="C389">
         <v>1028</v>
@@ -32265,7 +33002,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="C390">
         <v>1006</v>
@@ -32345,7 +33082,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>241</v>
+        <v>404</v>
       </c>
       <c r="C391">
         <v>848</v>
@@ -32425,7 +33162,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>242</v>
+        <v>405</v>
       </c>
       <c r="C392">
         <v>627</v>
@@ -32505,7 +33242,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>211</v>
+        <v>406</v>
       </c>
       <c r="C393">
         <v>772</v>
@@ -32585,7 +33322,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>243</v>
+        <v>407</v>
       </c>
       <c r="C394">
         <v>975</v>
@@ -32665,7 +33402,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>244</v>
+        <v>408</v>
       </c>
       <c r="C395">
         <v>834</v>
@@ -32745,7 +33482,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>245</v>
+        <v>409</v>
       </c>
       <c r="C396">
         <v>938</v>
@@ -32825,7 +33562,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>155</v>
+        <v>410</v>
       </c>
       <c r="C397">
         <v>805</v>
@@ -32905,7 +33642,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>156</v>
+        <v>411</v>
       </c>
       <c r="C398">
         <v>610</v>
@@ -32985,7 +33722,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>194</v>
+        <v>412</v>
       </c>
       <c r="C399">
         <v>912</v>
@@ -33065,7 +33802,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>36</v>
+        <v>413</v>
       </c>
       <c r="C400">
         <v>1093</v>
@@ -33145,7 +33882,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>211</v>
+        <v>414</v>
       </c>
       <c r="C401">
         <v>978</v>
@@ -33225,7 +33962,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="C402">
         <v>986</v>
@@ -33305,7 +34042,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>246</v>
+        <v>416</v>
       </c>
       <c r="C403">
         <v>843</v>
@@ -33385,7 +34122,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>41</v>
+        <v>417</v>
       </c>
       <c r="C404">
         <v>1107</v>
@@ -33465,7 +34202,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>42</v>
+        <v>418</v>
       </c>
       <c r="C405">
         <v>768</v>
@@ -33545,7 +34282,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>124</v>
+        <v>419</v>
       </c>
       <c r="C406">
         <v>584</v>
@@ -33625,7 +34362,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>125</v>
+        <v>420</v>
       </c>
       <c r="C407">
         <v>519</v>
@@ -33705,7 +34442,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>36</v>
+        <v>421</v>
       </c>
       <c r="C408">
         <v>922</v>
@@ -33785,7 +34522,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>25</v>
+        <v>422</v>
       </c>
       <c r="C409">
         <v>1096</v>
@@ -33865,7 +34602,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>247</v>
+        <v>423</v>
       </c>
       <c r="C410">
         <v>1108</v>
@@ -33945,7 +34682,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>18</v>
+        <v>424</v>
       </c>
       <c r="C411">
         <v>857</v>
@@ -34025,7 +34762,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="C412">
         <v>958</v>
@@ -34105,7 +34842,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>52</v>
+        <v>426</v>
       </c>
       <c r="C413">
         <v>1094</v>
@@ -34185,7 +34922,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>53</v>
+        <v>427</v>
       </c>
       <c r="C414">
         <v>985</v>
@@ -34265,7 +35002,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>35</v>
+        <v>428</v>
       </c>
       <c r="C415">
         <v>995</v>
@@ -34345,7 +35082,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="C416">
         <v>914</v>
@@ -34425,7 +35162,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="C417">
         <v>760</v>
@@ -34505,7 +35242,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>147</v>
+        <v>431</v>
       </c>
       <c r="C418">
         <v>497</v>
@@ -34585,7 +35322,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>195</v>
+        <v>432</v>
       </c>
       <c r="C419">
         <v>772</v>
@@ -34665,7 +35402,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>196</v>
+        <v>433</v>
       </c>
       <c r="C420">
         <v>797</v>
@@ -34745,7 +35482,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>26</v>
+        <v>434</v>
       </c>
       <c r="C421">
         <v>780</v>
@@ -34825,7 +35562,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>27</v>
+        <v>435</v>
       </c>
       <c r="C422">
         <v>843</v>
@@ -34905,7 +35642,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>48</v>
+        <v>436</v>
       </c>
       <c r="C423">
         <v>1157</v>
@@ -34985,7 +35722,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>248</v>
+        <v>437</v>
       </c>
       <c r="C424">
         <v>784</v>
@@ -35065,7 +35802,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>249</v>
+        <v>438</v>
       </c>
       <c r="C425">
         <v>1153</v>
@@ -35145,7 +35882,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>250</v>
+        <v>439</v>
       </c>
       <c r="C426">
         <v>907</v>
@@ -35225,7 +35962,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>251</v>
+        <v>440</v>
       </c>
       <c r="C427">
         <v>1082</v>
@@ -35305,7 +36042,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>26</v>
+        <v>441</v>
       </c>
       <c r="C428">
         <v>787</v>
@@ -35385,7 +36122,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>155</v>
+        <v>442</v>
       </c>
       <c r="C429">
         <v>658</v>
@@ -35465,7 +36202,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>156</v>
+        <v>443</v>
       </c>
       <c r="C430">
         <v>713</v>
@@ -35545,7 +36282,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>252</v>
+        <v>444</v>
       </c>
       <c r="C431">
         <v>1160</v>
@@ -35625,7 +36362,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>253</v>
+        <v>445</v>
       </c>
       <c r="C432">
         <v>634</v>
@@ -35705,7 +36442,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>254</v>
+        <v>446</v>
       </c>
       <c r="C433">
         <v>407</v>
@@ -35785,7 +36522,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>255</v>
+        <v>447</v>
       </c>
       <c r="C434">
         <v>631</v>
@@ -35865,7 +36602,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>256</v>
+        <v>448</v>
       </c>
       <c r="C435">
         <v>925</v>
@@ -35945,7 +36682,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>92</v>
+        <v>449</v>
       </c>
       <c r="C436">
         <v>780</v>
@@ -36025,7 +36762,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="C437">
         <v>960</v>
@@ -36105,7 +36842,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>35</v>
+        <v>451</v>
       </c>
       <c r="C438">
         <v>560</v>
@@ -36185,7 +36922,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>257</v>
+        <v>452</v>
       </c>
       <c r="C439">
         <v>825</v>
@@ -36265,7 +37002,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>258</v>
+        <v>453</v>
       </c>
       <c r="C440">
         <v>723</v>
@@ -36345,7 +37082,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>27</v>
+        <v>454</v>
       </c>
       <c r="C441">
         <v>735</v>
@@ -36425,7 +37162,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>27</v>
+        <v>455</v>
       </c>
       <c r="C442">
         <v>553</v>
@@ -36505,7 +37242,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>259</v>
+        <v>456</v>
       </c>
       <c r="C443">
         <v>1092</v>
@@ -36585,7 +37322,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>147</v>
+        <v>457</v>
       </c>
       <c r="C444">
         <v>914</v>
@@ -36665,7 +37402,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>260</v>
+        <v>458</v>
       </c>
       <c r="C445">
         <v>1036</v>
@@ -36745,7 +37482,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>261</v>
+        <v>459</v>
       </c>
       <c r="C446">
         <v>901</v>
@@ -36825,7 +37562,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>26</v>
+        <v>460</v>
       </c>
       <c r="C447">
         <v>844</v>
@@ -36905,7 +37642,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>27</v>
+        <v>461</v>
       </c>
       <c r="C448">
         <v>789</v>
@@ -36985,7 +37722,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="C449">
         <v>1069</v>
@@ -37065,7 +37802,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>26</v>
+        <v>463</v>
       </c>
       <c r="C450">
         <v>866</v>
@@ -37145,7 +37882,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>27</v>
+        <v>464</v>
       </c>
       <c r="C451">
         <v>769</v>
@@ -37225,7 +37962,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>20</v>
+        <v>465</v>
       </c>
       <c r="C452">
         <v>497</v>
@@ -37305,7 +38042,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>41</v>
+        <v>466</v>
       </c>
       <c r="C453">
         <v>746</v>
@@ -37385,7 +38122,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>42</v>
+        <v>467</v>
       </c>
       <c r="C454">
         <v>890</v>
@@ -37465,7 +38202,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>26</v>
+        <v>468</v>
       </c>
       <c r="C455">
         <v>1058</v>
@@ -37545,7 +38282,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>27</v>
+        <v>469</v>
       </c>
       <c r="C456">
         <v>1093</v>
@@ -37625,7 +38362,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>262</v>
+        <v>470</v>
       </c>
       <c r="C457">
         <v>633</v>
@@ -37705,7 +38442,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>18</v>
+        <v>471</v>
       </c>
       <c r="C458">
         <v>941</v>
@@ -37785,7 +38522,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="C459">
         <v>1012</v>
@@ -37865,7 +38602,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>263</v>
+        <v>473</v>
       </c>
       <c r="C460">
         <v>1036</v>
@@ -37945,7 +38682,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>264</v>
+        <v>474</v>
       </c>
       <c r="C461">
         <v>1117</v>
@@ -38025,7 +38762,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>45</v>
+        <v>475</v>
       </c>
       <c r="C462">
         <v>720</v>
@@ -38105,7 +38842,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="C463">
         <v>621</v>
